--- a/docs/项目API清单.xlsx
+++ b/docs/项目API清单.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="API接口总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="字段明细" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="返回字段说明" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="风控参数说明" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="返回字段分类" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="API接口总览" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="返回字段说明" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风控参数说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="返回字段分类" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -54,7 +54,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -68,17 +68,34 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -445,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -614,6 +631,391 @@
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>lastSrcChannelId1=2为搜索渠道；返回68列字段含SPU维度数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>京麦订单明细-创建导出任务</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>https://sff.jd.com/api?v=1.0&amp;appId=CQLEJWPYPFOVQBC8UFLQ&amp;api=dsm.order.export.exportCenterService.createdExportTask</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>sff.jd.com</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>京麦订单导出页面创建加密导出任务（5步异步链路第1步）</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>python main.py --biz_key '京麦订单明细_创建任务' --date YYYY-MM-DD --h5st '&lt;h5st&gt;'</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>JSON（code/msg/dsm-trace-id）</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>时间跨度≤31天；两次间隔≥10分钟；单日≤10次</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>无固定限制（按业务硬性约束）</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>main.py class JingMaiOrderExportAPI.create_export_task</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>京麦订单明细-查询任务列表（轮询）</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://sff.jd.com/api?v=1.0&amp;appId=CQLEJWPYPFOVQBC8UFLQ&amp;api=dsm.order.export.exportCenterService.queryExportTaskInfo</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>sff.jd.com</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>分页查询任务列表，按 startTime/endTime 匹配刚创建的任务拿 taskId（5步第2步）</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>create_export_task 后自动调</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>JSON（data.itemList[] 含 taskStatus / taskData.startTime / taskData.endTime）</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>pageSize ≤ 10（足够覆盖最近操作）</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>3s × 20次 = 60s 超时（轮询循环）</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>main.py class JingMaiOrderExportAPI.wait_for_task_ready</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>京麦订单明细-下载加密 zip</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://export.shop.jd.com/exportCenter/export.action?taskId={taskId}</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>export.shop.jd.com</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>下载加密 zip（含订单数据，password 加密，5步第3步）</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>wait_for_task_ready 返回 taskStatus=2 后自动调</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>application/octet-stream（PK\x03\x04 开头）</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Content-Length ≥ 1KB（&lt;1KB 视为下载失败）</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>无固定限制（GET 静态下载）</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>main.py class JingMaiOrderExportAPI.download_encrypted_zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>京麦订单明细-申请解压密码短信</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://sff.jd.com/api?v=1.0&amp;appId=CQLEJWPYPFOVQBC8UFLQ&amp;api=dsm.order.export.exportCenterService.exportTaskPwdSend</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>sff.jd.com</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>触发短信下发解压密码（5步第4步，接口不返回密码明文）</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>create_wait_and_download 后自动调</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>JSON（data 是字符串，含「密码短信发送成功!当前任务剩余短信发送次数N次」）</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>单 taskId 两次申请≥60秒；单 taskId 单日≤10次</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>无固定限制（按业务硬性约束）</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>main.py class JingMaiOrderExportAPI.request_export_password</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>京麦订单明细-IMAP 监听拿密码</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>imap.qq.com:993（IMAP SSL）</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>IMAP</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>imap.qq.com</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>监听 QQ 邮箱（iPhone 快捷指令自动转发短信）拿解压密码（5步第5步前半）</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>request_export_password 后自动调（5分钟超时降级保留 zip）</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>QQ 邮箱邮件内容（主题「京东密码转发」+ 正文纯密码或带 taskId 标记）</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>iPhone 快捷指令投递间隔通常 30-60s</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>5s × 60次 = 300s 超时（监听循环）</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>main.py class JingMaiOrderExportAPI.fetch_password_from_imap</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>京麦订单明细-双层解密+转 xlsx+Excel 后置</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>本地 zipfile + msoffcrypto（无网络）</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>本地解密</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>本地</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>解开 zip 拿到加密 xls → msoffcrypto 用密码二次解密 → 读 xlsx → Excel 后置统一规则（日期列/SKU整数0/订单编号@）→ 删除中间 zip（5步第5步后半）</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>fetch_password_from_imap 拿到密码后自动调</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>output/京麦订单明细/{date}/订单明细_{date}.xlsx</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>无（本地处理）</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>无（本地处理）</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>main.py class JingMaiOrderExportAPI.extract_xlsx_from_zip</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>京麦订单明细-业务汇总（5步一键）</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>本地（JingMaiOrderExportAPI.run_full_export 编排）</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>本地编排</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>本地</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>完整 5 步一键：创建→轮询→下载→短信→IMAP→双层解密→Excel 后置（终极入口）</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>python main.py --biz_key '京麦订单明细_完整一键导出' --date YYYY-MM-DD --h5st '&lt;h5st&gt;'</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>dict（code/msg/taskId/zip_path/xlsx_path/password/password_source）</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>无（5步链路综合）</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>无（5步链路综合）</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>main.py class JingMaiOrderExportAPI.run_full_export + _run_jm_run_full_export</t>
         </is>
       </c>
     </row>
